--- a/Data Catalog.xlsx
+++ b/Data Catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Documents\hillsborogis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0197C0-5AA6-4ABD-BE0E-48C3BD107B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFE81CA-EEEC-4E2B-B1A9-162B82212A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14700" yWindow="0" windowWidth="14805" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datasets" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="166">
   <si>
     <t>relationship_id</t>
   </si>
@@ -883,6 +883,9 @@
   </si>
   <si>
     <t>All buildings in HIL-006 exist outside city limits</t>
+  </si>
+  <si>
+    <t>SFR zones omit the "SF" prefix within the dataset</t>
   </si>
 </sst>
 </file>
@@ -32343,7 +32346,17 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>165</v>
+      </c>
+    </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
